--- a/it.xlsx
+++ b/it.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\design22\Desktop\CPP\bai2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D77A05-19C0-4B66-B1FC-3151CF8F6417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA3DDC7-4732-4436-AF2C-6CA765E017FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="581" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="581" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="専門用語" sheetId="1" r:id="rId1"/>
@@ -20,9 +20,10 @@
     <sheet name="OPP" sheetId="2" r:id="rId5"/>
     <sheet name="git" sheetId="4" r:id="rId6"/>
     <sheet name="Sourcetree" sheetId="5" r:id="rId7"/>
-    <sheet name="PRJ" sheetId="8" r:id="rId8"/>
-    <sheet name="Sheet6" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet name="イメージ" sheetId="10" r:id="rId10"/>
+    <sheet name="Vu" sheetId="11" r:id="rId8"/>
+    <sheet name="PRJ" sheetId="8" state="hidden" r:id="rId9"/>
+    <sheet name="Sheet6" sheetId="9" state="hidden" r:id="rId10"/>
+    <sheet name="イメージ" sheetId="10" state="hidden" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="623">
   <si>
     <t>オブジェクト指向</t>
     <phoneticPr fontId="1"/>
@@ -16067,12 +16068,224 @@
     <t>-27.2</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>nhà</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ngoài ra</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FPT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>v</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ề</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ư</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ớ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>c</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>công tác</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>tìm hiểu trước DD nó làm cái gì </t>
+  </si>
+  <si>
+    <t>UT (単体テスト) IT (結合テスト）</t>
+  </si>
+  <si>
+    <t>DD（詳細設計）</t>
+  </si>
+  <si>
+    <t>V字モデルとは？システム開発の基本を理解しよう</t>
+  </si>
+  <si>
+    <t>đọc để biết V model trong sản xuất phần mềm.</t>
+  </si>
+  <si>
+    <t>xử lý mấy tình huống xử lý vấn đề với vai trò là leader</t>
+  </si>
+  <si>
+    <r>
+      <t>xem tr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ư</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ớc quy trình sản xuất phần mềm có gì đặc biệt không.</t>
+    </r>
+  </si>
+  <si>
+    <t>HT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>有給</t>
+    <rPh sb="0" eb="2">
+      <t>ユウキュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>他の休暇</t>
+    <rPh sb="0" eb="1">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キュウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>年休</t>
+    <rPh sb="0" eb="2">
+      <t>ネンキュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>ĐI L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Ạ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">I </t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14x2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2x2km</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>TĂNG L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ƯƠ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NG</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1.3-1.5M</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>????</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -16304,6 +16517,41 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -16349,7 +16597,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -16771,12 +17019,68 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -16894,6 +17198,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -16939,33 +17280,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -17526,6 +17841,143 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>518160</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>328341</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>129977</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99ED5810-6CF8-AA46-09C3-14240EC686BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="518160" y="1600200"/>
+          <a:ext cx="7856901" cy="5044877"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>598716</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>54430</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>609601</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>183958</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2620AB37-D89E-3572-79B4-C6878168C863}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8578934" y="1661557"/>
+          <a:ext cx="9321140" cy="5546656"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>119744</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>385542</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>57259</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7404919-389A-2AF5-5345-26F165E037BF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8893630" y="7239000"/>
+          <a:ext cx="5665112" cy="1788088"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
@@ -17703,7 +18155,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -17731,8 +18183,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1971624" y="738110"/>
-          <a:ext cx="6565707" cy="3224290"/>
+          <a:off x="1975434" y="711216"/>
+          <a:ext cx="6521556" cy="3098784"/>
           <a:chOff x="2651067" y="553143"/>
           <a:chExt cx="6542690" cy="3115044"/>
         </a:xfrm>
@@ -20214,8 +20666,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3767418" y="7945530"/>
-          <a:ext cx="1654661" cy="240477"/>
+          <a:off x="3755876" y="7704155"/>
+          <a:ext cx="1648946" cy="244624"/>
           <a:chOff x="3182471" y="8075855"/>
           <a:chExt cx="1650851" cy="229608"/>
         </a:xfrm>
@@ -21087,6 +21539,17 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2FB2870-6B7B-4CE2-97BE-5D2D9BA3C792}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F716D66-29DD-4818-92BA-22DFCDB2AE79}">
   <dimension ref="B2:J39"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -21103,14 +21566,14 @@
       <c r="E2" s="27" t="s">
         <v>565</v>
       </c>
-      <c r="F2" s="60" t="s">
+      <c r="F2" s="55" t="s">
         <v>560</v>
       </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="62" t="s">
+      <c r="G2" s="56"/>
+      <c r="H2" s="57" t="s">
         <v>566</v>
       </c>
-      <c r="I2" s="63"/>
+      <c r="I2" s="58"/>
       <c r="J2" s="26" t="s">
         <v>567</v>
       </c>
@@ -21148,61 +21611,61 @@
       <c r="E23" s="27" t="s">
         <v>565</v>
       </c>
-      <c r="F23" s="60" t="s">
+      <c r="F23" s="55" t="s">
         <v>559</v>
       </c>
-      <c r="G23" s="61"/>
-      <c r="H23" s="62" t="s">
+      <c r="G23" s="56"/>
+      <c r="H23" s="57" t="s">
         <v>566</v>
       </c>
-      <c r="I23" s="63"/>
+      <c r="I23" s="58"/>
       <c r="J23" s="26" t="s">
         <v>567</v>
       </c>
     </row>
     <row r="24" spans="4:10" ht="18.600000000000001" thickBot="1"/>
     <row r="25" spans="4:10" ht="18.600000000000001" thickBot="1">
-      <c r="D25" s="57" t="s">
+      <c r="D25" s="74" t="s">
         <v>569</v>
       </c>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="51" t="s">
+      <c r="E25" s="75"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="68" t="s">
         <v>559</v>
       </c>
-      <c r="I25" s="52"/>
-      <c r="J25" s="53"/>
+      <c r="I25" s="69"/>
+      <c r="J25" s="70"/>
     </row>
     <row r="26" spans="4:10">
-      <c r="D26" s="47" t="s">
+      <c r="D26" s="64" t="s">
         <v>570</v>
       </c>
-      <c r="E26" s="48"/>
+      <c r="E26" s="65"/>
       <c r="F26" s="30">
         <v>10</v>
       </c>
       <c r="G26" s="31" t="s">
         <v>581</v>
       </c>
-      <c r="H26" s="67" t="s">
+      <c r="H26" s="45" t="s">
         <v>589</v>
       </c>
       <c r="I26" s="42"/>
       <c r="J26" s="43"/>
     </row>
     <row r="27" spans="4:10" ht="18.600000000000001" thickBot="1">
-      <c r="D27" s="45" t="s">
+      <c r="D27" s="62" t="s">
         <v>571</v>
       </c>
-      <c r="E27" s="46"/>
+      <c r="E27" s="63"/>
       <c r="F27" s="21">
         <v>15</v>
       </c>
       <c r="G27" s="32" t="s">
         <v>582</v>
       </c>
-      <c r="H27" s="68" t="s">
+      <c r="H27" s="46" t="s">
         <v>590</v>
       </c>
       <c r="I27" s="44" t="s">
@@ -21211,27 +21674,27 @@
       <c r="J27" s="39"/>
     </row>
     <row r="28" spans="4:10" ht="18.600000000000001" thickBot="1">
-      <c r="D28" s="45" t="s">
+      <c r="D28" s="62" t="s">
         <v>572</v>
       </c>
-      <c r="E28" s="46"/>
+      <c r="E28" s="63"/>
       <c r="F28" s="21">
         <v>40</v>
       </c>
       <c r="G28" s="32" t="s">
         <v>583</v>
       </c>
-      <c r="H28" s="54" t="s">
+      <c r="H28" s="71" t="s">
         <v>592</v>
       </c>
-      <c r="I28" s="55"/>
-      <c r="J28" s="56"/>
+      <c r="I28" s="72"/>
+      <c r="J28" s="73"/>
     </row>
     <row r="29" spans="4:10">
-      <c r="D29" s="45" t="s">
+      <c r="D29" s="62" t="s">
         <v>573</v>
       </c>
-      <c r="E29" s="46"/>
+      <c r="E29" s="63"/>
       <c r="F29" s="21">
         <v>30</v>
       </c>
@@ -21249,10 +21712,10 @@
       </c>
     </row>
     <row r="30" spans="4:10">
-      <c r="D30" s="45" t="s">
+      <c r="D30" s="62" t="s">
         <v>574</v>
       </c>
-      <c r="E30" s="46"/>
+      <c r="E30" s="63"/>
       <c r="F30" s="21">
         <v>1</v>
       </c>
@@ -21270,10 +21733,10 @@
       </c>
     </row>
     <row r="31" spans="4:10">
-      <c r="D31" s="45" t="s">
+      <c r="D31" s="62" t="s">
         <v>575</v>
       </c>
-      <c r="E31" s="46"/>
+      <c r="E31" s="63"/>
       <c r="F31" s="21">
         <v>10</v>
       </c>
@@ -21291,10 +21754,10 @@
       </c>
     </row>
     <row r="32" spans="4:10" ht="18.600000000000001" thickBot="1">
-      <c r="D32" s="45" t="s">
+      <c r="D32" s="62" t="s">
         <v>576</v>
       </c>
-      <c r="E32" s="46"/>
+      <c r="E32" s="63"/>
       <c r="F32" s="21">
         <v>20</v>
       </c>
@@ -21312,27 +21775,27 @@
       </c>
     </row>
     <row r="33" spans="4:10" ht="18.600000000000001" thickBot="1">
-      <c r="D33" s="45" t="s">
+      <c r="D33" s="62" t="s">
         <v>577</v>
       </c>
-      <c r="E33" s="46"/>
+      <c r="E33" s="63"/>
       <c r="F33" s="21">
         <v>3</v>
       </c>
       <c r="G33" s="32" t="s">
         <v>588</v>
       </c>
-      <c r="H33" s="64" t="s">
+      <c r="H33" s="59" t="s">
         <v>597</v>
       </c>
-      <c r="I33" s="65"/>
-      <c r="J33" s="66"/>
+      <c r="I33" s="60"/>
+      <c r="J33" s="61"/>
     </row>
     <row r="34" spans="4:10">
-      <c r="D34" s="45" t="s">
+      <c r="D34" s="62" t="s">
         <v>578</v>
       </c>
-      <c r="E34" s="46"/>
+      <c r="E34" s="63"/>
       <c r="F34" s="21" t="s">
         <v>580</v>
       </c>
@@ -21344,10 +21807,10 @@
       <c r="J34" s="40"/>
     </row>
     <row r="35" spans="4:10" ht="18.600000000000001" thickBot="1">
-      <c r="D35" s="49" t="s">
+      <c r="D35" s="66" t="s">
         <v>579</v>
       </c>
-      <c r="E35" s="50"/>
+      <c r="E35" s="67"/>
       <c r="F35" s="29"/>
       <c r="G35" s="29"/>
       <c r="H35" s="37" t="s">
@@ -21383,11 +21846,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H33:J33"/>
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="D26:E26"/>
     <mergeCell ref="D35:E35"/>
@@ -21401,6 +21859,11 @@
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H33:J33"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21410,122 +21873,316 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91B58131-D9DD-431F-8B2A-BF3ADE3E3655}">
-  <dimension ref="C2:E15"/>
+  <dimension ref="B1:I22"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:5">
-      <c r="C2" t="s">
+    <row r="1" spans="3:8" ht="18.600000000000001" thickBot="1">
+      <c r="D1" t="s">
+        <v>613</v>
+      </c>
+      <c r="G1" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="2" spans="3:8">
+      <c r="C2" s="47" t="s">
         <v>304</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="47">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="3:5">
-      <c r="C3" t="s">
+      <c r="E2" s="47"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="47">
+        <v>33</v>
+      </c>
+      <c r="H2" s="47"/>
+    </row>
+    <row r="3" spans="3:8">
+      <c r="C3" s="48" t="s">
         <v>305</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="48">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="3:5">
-      <c r="C4" t="s">
+      <c r="E3" s="48"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="48">
+        <v>0</v>
+      </c>
+      <c r="H3" s="48"/>
+    </row>
+    <row r="4" spans="3:8">
+      <c r="C4" s="48" t="s">
+        <v>601</v>
+      </c>
+      <c r="D4" s="48">
+        <v>0</v>
+      </c>
+      <c r="E4" s="48"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="48">
+        <v>3</v>
+      </c>
+      <c r="H4" s="48"/>
+    </row>
+    <row r="5" spans="3:8">
+      <c r="C5" s="48" t="s">
         <v>306</v>
       </c>
-      <c r="D4">
+      <c r="D5" s="48">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="5" spans="3:5">
-      <c r="C5" t="s">
+      <c r="E5" s="48"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="48">
+        <v>3</v>
+      </c>
+      <c r="H5" s="48"/>
+    </row>
+    <row r="6" spans="3:8">
+      <c r="C6" s="48" t="s">
         <v>307</v>
       </c>
-      <c r="D5">
+      <c r="D6" s="48">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="3:5">
-      <c r="C6" t="s">
+      <c r="E6" s="48"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="48">
+        <v>0</v>
+      </c>
+      <c r="H6" s="48"/>
+    </row>
+    <row r="7" spans="3:8">
+      <c r="C7" s="48" t="s">
         <v>315</v>
       </c>
-      <c r="D6">
+      <c r="D7" s="48">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="7" spans="3:5">
-      <c r="C7" t="s">
+      <c r="E7" s="48"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="48">
+        <v>0.7</v>
+      </c>
+      <c r="H7" s="48"/>
+    </row>
+    <row r="8" spans="3:8">
+      <c r="C8" s="48" t="s">
         <v>308</v>
       </c>
-      <c r="D7">
-        <f>SUM(D2:D6)</f>
+      <c r="D8" s="48">
+        <f>SUM(D2:D7)</f>
         <v>34</v>
       </c>
-      <c r="E7">
-        <f>D7*12</f>
+      <c r="E8" s="48">
+        <f>D8*12</f>
         <v>408</v>
       </c>
-    </row>
-    <row r="9" spans="3:5">
-      <c r="C9" t="s">
+      <c r="F8" s="50"/>
+      <c r="G8" s="48">
+        <f>SUM(G2:G7)</f>
+        <v>39.700000000000003</v>
+      </c>
+      <c r="H8" s="48">
+        <f>G8*12</f>
+        <v>476.40000000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="3:8">
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+    </row>
+    <row r="10" spans="3:8">
+      <c r="C10" s="48" t="s">
         <v>309</v>
       </c>
-      <c r="D9">
+      <c r="D10" s="48">
         <v>0.23</v>
       </c>
-    </row>
-    <row r="10" spans="3:5">
-      <c r="C10" t="s">
+      <c r="E10" s="48"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+    </row>
+    <row r="11" spans="3:8">
+      <c r="C11" s="48" t="s">
         <v>310</v>
       </c>
-      <c r="D10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="3:5">
-      <c r="C11" t="s">
+      <c r="D11" s="77">
+        <v>10</v>
+      </c>
+      <c r="E11" s="48"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="48">
+        <v>25</v>
+      </c>
+      <c r="H11" s="48"/>
+    </row>
+    <row r="12" spans="3:8">
+      <c r="C12" s="48" t="s">
         <v>311</v>
       </c>
-      <c r="D11">
-        <f>D10*D9</f>
-        <v>4.6000000000000005</v>
-      </c>
-      <c r="E11">
-        <f>D11*12</f>
-        <v>55.2</v>
-      </c>
-    </row>
-    <row r="12" spans="3:5">
-      <c r="C12" t="s">
+      <c r="D12" s="48">
+        <f>D11*D10</f>
+        <v>2.3000000000000003</v>
+      </c>
+      <c r="E12" s="48">
+        <f>D12*12</f>
+        <v>27.6</v>
+      </c>
+      <c r="F12" s="50"/>
+      <c r="G12" s="48">
+        <v>6.4</v>
+      </c>
+      <c r="H12" s="48">
+        <f>G12*12</f>
+        <v>76.800000000000011</v>
+      </c>
+    </row>
+    <row r="13" spans="3:8">
+      <c r="C13" s="48" t="s">
         <v>312</v>
       </c>
-      <c r="D12">
+      <c r="D13" s="48">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="13" spans="3:5">
-      <c r="C13" t="s">
+      <c r="E13" s="48"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="48">
+        <v>2</v>
+      </c>
+      <c r="H13" s="48"/>
+    </row>
+    <row r="14" spans="3:8">
+      <c r="C14" s="48" t="s">
         <v>313</v>
       </c>
-      <c r="D13">
-        <f>D12*D2</f>
+      <c r="D14" s="48">
+        <f>D13*D2</f>
         <v>135</v>
       </c>
-      <c r="E13">
-        <f>D13</f>
+      <c r="E14" s="48">
+        <f>D14</f>
         <v>135</v>
       </c>
-    </row>
-    <row r="15" spans="3:5">
-      <c r="C15" t="s">
+      <c r="F14" s="50"/>
+      <c r="G14" s="48">
+        <f>G2*G13</f>
+        <v>66</v>
+      </c>
+      <c r="H14" s="48">
+        <f>G14</f>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="3:8">
+      <c r="C15" s="48" t="s">
+        <v>602</v>
+      </c>
+      <c r="D15" s="48" t="s">
+        <v>605</v>
+      </c>
+      <c r="E15" s="48">
+        <v>1</v>
+      </c>
+      <c r="F15" s="50"/>
+      <c r="G15" s="48" t="s">
+        <v>604</v>
+      </c>
+      <c r="H15" s="48">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="3:8">
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="48"/>
+    </row>
+    <row r="17" spans="2:9" ht="18.600000000000001" thickBot="1">
+      <c r="C17" s="49" t="s">
         <v>314</v>
       </c>
-      <c r="E15">
-        <f>SUM(E7:E13)</f>
-        <v>598.20000000000005</v>
+      <c r="D17" s="49"/>
+      <c r="E17" s="49">
+        <f>SUM(E8:E15)</f>
+        <v>571.6</v>
+      </c>
+      <c r="F17" s="50"/>
+      <c r="G17" s="49"/>
+      <c r="H17" s="49">
+        <f>SUM(H8:H15)</f>
+        <v>627.20000000000005</v>
+      </c>
+      <c r="I17">
+        <f>H17-E17</f>
+        <v>55.600000000000023</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" t="s">
+        <v>614</v>
+      </c>
+      <c r="D18">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" t="s">
+        <v>615</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" t="s">
+        <v>616</v>
+      </c>
+      <c r="D20">
+        <v>115</v>
+      </c>
+      <c r="H20">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9">
+      <c r="B21" t="s">
+        <v>617</v>
+      </c>
+      <c r="D21" t="s">
+        <v>619</v>
+      </c>
+      <c r="H21" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22" t="s">
+        <v>620</v>
+      </c>
+      <c r="D22" t="s">
+        <v>621</v>
+      </c>
+      <c r="H22" t="s">
+        <v>622</v>
       </c>
     </row>
   </sheetData>
@@ -23918,6 +24575,60 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58054683-1CB8-4966-9B64-09F4AD337043}">
+  <dimension ref="B2:N32"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="2" spans="2:14" ht="22.2">
+      <c r="B2" s="52" t="s">
+        <v>606</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" ht="26.4">
+      <c r="N3" s="53" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" ht="20.399999999999999">
+      <c r="B4" s="51" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" ht="20.399999999999999">
+      <c r="B6" s="51" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14">
+      <c r="B7" s="15"/>
+    </row>
+    <row r="8" spans="2:14">
+      <c r="B8" s="15"/>
+    </row>
+    <row r="31" spans="2:2" ht="28.8">
+      <c r="B31" s="54" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" ht="28.8">
+      <c r="B32" s="54" t="s">
+        <v>611</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="N2" r:id="rId1" display="https://products.sint.co.jp/ober/blog/v-model" xr:uid="{36CEA404-CA8B-49EA-9979-BEEDD9044306}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F46C5190-89F8-4312-8F7A-B6428DC7F9CB}">
   <dimension ref="B2:I82"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -24259,15 +24970,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2FB2870-6B7B-4CE2-97BE-5D2D9BA3C792}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18"/>
-  <sheetData/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>